--- a/artfynd/A 8878-2026 artfynd.xlsx
+++ b/artfynd/A 8878-2026 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>131047924</v>
       </c>
       <c r="B3" t="n">
-        <v>57064</v>
+        <v>57066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>131048562</v>
       </c>
       <c r="B4" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8878-2026 artfynd.xlsx
+++ b/artfynd/A 8878-2026 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>131047924</v>
       </c>
       <c r="B3" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>131048562</v>
       </c>
       <c r="B4" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
